--- a/words.xlsx
+++ b/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA5A529-2764-BA40-969A-844530B3FBC0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02447F6-3117-C045-9C27-070B37BB0A77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -82,6 +82,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="12"/>
@@ -125,7 +128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -444,6 +447,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">

--- a/words.xlsx
+++ b/words.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02447F6-3117-C045-9C27-070B37BB0A77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C45FC5BD-AE57-A640-94AB-E7CFE72F2566}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="380" yWindow="460" windowWidth="24820" windowHeight="15020" xr2:uid="{90F29878-E095-0247-8CA8-B281629F062F}"/>
   </bookViews>
@@ -25,17 +25,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>word</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>meaning</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>date</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -82,9 +78,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-  </numFmts>
   <fonts count="2">
     <font>
       <sz val="12"/>
@@ -124,11 +117,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -445,76 +435,55 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{527ABE91-7216-BA4F-A91C-2F06E544A41C}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="11.33203125" style="1" bestFit="1" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B3" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1">
-        <v>46093</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="1">
-        <v>46094</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>11</v>
-      </c>
-      <c r="C5" s="1">
-        <v>46095</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1">
-        <v>46095</v>
       </c>
     </row>
   </sheetData>
